--- a/exp/jack/Data/UK_Data/UK_Materials.xlsx
+++ b/exp/jack/Data/UK_Data/UK_Materials.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofcambridgecloud-my.sharepoint.com/personal/jjjl4_cam_ac_uk/Documents/1. Cambridge/1. PhD/1. Projects/10.EP/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/JackLynch/CUBES/exp/jack/Data/UK_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A903F9DB-1853-BD49-924A-655394991B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98CF570-FDCD-D449-8C8D-C2B9C70E815D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="1620" windowWidth="38400" windowHeight="21140" xr2:uid="{33685054-C986-9945-9299-7AF44BC59D3F}"/>
   </bookViews>
@@ -38,9 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
   <si>
-    <t>Materials</t>
-  </si>
-  <si>
     <t>Clay tile - hollow - 2 cells deep - 200mm</t>
   </si>
   <si>
@@ -120,22 +117,17 @@
   </si>
   <si>
     <t>Smooth</t>
+  </si>
+  <si>
+    <t>Material</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -148,14 +140,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -186,14 +170,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -522,46 +502,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>0.33</v>
@@ -584,7 +564,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3">
         <v>0.15</v>
@@ -596,7 +576,7 @@
         <v>1630</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G3">
         <v>0.9</v>
@@ -616,7 +596,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4">
         <v>0.57999999999999996</v>
@@ -628,7 +608,7 @@
         <v>1090</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G4">
         <v>0.9</v>
@@ -648,7 +628,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5">
         <v>3.5999999999999997E-2</v>
@@ -660,7 +640,7 @@
         <v>960</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5">
         <v>0.9</v>
@@ -680,10 +660,10 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F6">
         <v>2.5999999999999999E-2</v>
@@ -706,7 +686,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7">
         <v>1.45</v>
@@ -718,7 +698,7 @@
         <v>900</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G7">
         <v>0.9</v>
@@ -738,7 +718,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8">
         <v>0.53</v>
@@ -750,7 +730,7 @@
         <v>840</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G8">
         <v>0.9</v>
@@ -770,7 +750,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9">
         <v>0.18</v>
@@ -784,7 +764,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10">
         <v>1.34</v>
@@ -796,7 +776,7 @@
         <v>790</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G10">
         <v>0.9</v>
@@ -816,7 +796,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11">
         <v>0.15</v>
@@ -830,7 +810,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12">
         <v>0.67500000000000004</v>
@@ -842,7 +822,7 @@
         <v>790</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G12">
         <v>0.9</v>
@@ -862,7 +842,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13">
         <v>0.49</v>
@@ -874,7 +854,7 @@
         <v>880</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G13">
         <v>0.9</v>
@@ -894,7 +874,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <v>0.105</v>
@@ -906,7 +886,7 @@
         <v>130</v>
       </c>
       <c r="E14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G14">
         <v>0.9</v>
